--- a/currentbuild/StructureDefinition-npr-episode-identifier.xlsx
+++ b/currentbuild/StructureDefinition-npr-episode-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T09:28:38+00:00</t>
+    <t>2026-09-21T06:14:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-npr-episode-identifier.xlsx
+++ b/currentbuild/StructureDefinition-npr-episode-identifier.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.4</t>
+    <t>1.1.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T06:14:41+00:00</t>
+    <t>2026-09-21T06:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-npr-episode-identifier.xlsx
+++ b/currentbuild/StructureDefinition-npr-episode-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T06:15:47+00:00</t>
+    <t>2026-09-21T06:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-npr-episode-identifier.xlsx
+++ b/currentbuild/StructureDefinition-npr-episode-identifier.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.6</t>
+    <t>1.1.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T08:53:26+00:00</t>
+    <t>2026-10-07T09:44:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-npr-episode-identifier.xlsx
+++ b/currentbuild/StructureDefinition-npr-episode-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T09:44:04+00:00</t>
+    <t>2026-10-09T08:26:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-npr-episode-identifier.xlsx
+++ b/currentbuild/StructureDefinition-npr-episode-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T08:26:09+00:00</t>
+    <t>2026-10-09T09:36:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-npr-episode-identifier.xlsx
+++ b/currentbuild/StructureDefinition-npr-episode-identifier.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:50:47+00:00</t>
+    <t>2026-10-20T08:54:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
